--- a/Aeolus-Wireframe-06.xlsx
+++ b/Aeolus-Wireframe-06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cld\Aeolus-Tire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B84197-2F13-4C6A-AAFF-89D58F399BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F9188E-EA57-44F6-B472-4EA0599FCEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18936" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Support" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4373" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4334" uniqueCount="685">
   <si>
     <t>Tire Name</t>
   </si>
@@ -1763,9 +1763,6 @@
     <t>Notes:</t>
   </si>
   <si>
-    <t>Neo Fuel s</t>
-  </si>
-  <si>
     <t>NEO SERIES LONG HAUL:</t>
   </si>
   <si>
@@ -2037,6 +2034,66 @@
   </si>
   <si>
     <t>154/150L</t>
+  </si>
+  <si>
+    <t>7 tires: ASR65, ATR65, Neo Allroads T3, Neo Icedrive, Neo Winter D, Neo Urban D, and Neo Fuel S+ from this spec list are not in the catalog or website</t>
+  </si>
+  <si>
+    <t>bg-long-haul-premium</t>
+  </si>
+  <si>
+    <t>bg-reg-premium</t>
+  </si>
+  <si>
+    <t>bg-off-road-premium</t>
+  </si>
+  <si>
+    <t>bg-winter-premium</t>
+  </si>
+  <si>
+    <t>bg-urban-premium</t>
+  </si>
+  <si>
+    <t>bg-long-haul</t>
+  </si>
+  <si>
+    <t>bg-reg</t>
+  </si>
+  <si>
+    <t>bg-off-road</t>
+  </si>
+  <si>
+    <t>bg-winter</t>
+  </si>
+  <si>
+    <t>Neo-Fuel-Tplus-f1</t>
+  </si>
+  <si>
+    <t>Neo-Fuel-Tplus-f2</t>
+  </si>
+  <si>
+    <t>Neo-Fuel-Tplus-f3</t>
+  </si>
+  <si>
+    <t>Neo-Allroads-Splus-f1</t>
+  </si>
+  <si>
+    <t>Neo-Allroads-Splus-f2</t>
+  </si>
+  <si>
+    <t>Neo-Allroads-Dplus-f1</t>
+  </si>
+  <si>
+    <t>Neo-Allroads-Dplus-f2</t>
+  </si>
+  <si>
+    <t>Neo-Allroads-Dplus-f3</t>
+  </si>
+  <si>
+    <t>Neo-Construct-D-f1</t>
+  </si>
+  <si>
+    <t>Neo-Construct-D-f2</t>
   </si>
 </sst>
 </file>
@@ -2838,15 +2895,6 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2861,6 +2909,15 @@
     </xf>
     <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3167,753 +3224,464 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:J67"/>
+  <dimension ref="B1:L47"/>
   <sheetFormatPr defaultColWidth="15.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="1.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="1.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="1.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" style="1" customWidth="1"/>
-    <col min="12" max="13" width="23.6640625" style="1" customWidth="1"/>
-    <col min="14" max="21" width="15.44140625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="15.44140625" style="1"/>
+    <col min="2" max="2" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="1.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" style="1" customWidth="1"/>
+    <col min="13" max="14" width="23.6640625" style="1" customWidth="1"/>
+    <col min="15" max="22" width="15.44140625" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="15.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="60" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" s="60" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="60" t="s">
         <v>571</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="F1" s="60" t="s">
         <v>572</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="K1" s="60" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="2" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:11" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="E3" s="63"/>
+      <c r="F3" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="C3" s="1">
-        <v>8</v>
-      </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="68"/>
+      <c r="H3" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="7" t="s">
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F5" s="1" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F6" s="1" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="C5" s="1">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="K6" s="76" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F7" s="1" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="C6" s="1">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="J6" s="76" t="s">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="67"/>
+      <c r="H8" s="7" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
+      <c r="K8" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F10" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="E13" s="71"/>
+      <c r="F13" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F15" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J15" s="77"/>
+      <c r="K15" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F16" s="72" t="s">
+        <v>229</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="J16" s="77"/>
+      <c r="K16" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F17" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F18" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F19" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="20" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F20" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="G20" s="64"/>
+      <c r="H20" s="7" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="21" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F21" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="22" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="H22" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="23" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E23" s="64"/>
+      <c r="F23" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="24" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F24" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="1">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="1">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="67"/>
-      <c r="G8" s="7" t="s">
-        <v>583</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
+      <c r="L24" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="25" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F25" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>594</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="1">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+      <c r="L25" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="26" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="H26" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="1">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+      <c r="L26" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="27" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E27" s="65"/>
+      <c r="F27" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="1">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="1" t="s">
+      <c r="L27" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F28" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C12" s="1">
-        <v>12</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
+      <c r="L28" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="29" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F29" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G29" s="65"/>
+      <c r="H29" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="1">
-        <v>13</v>
-      </c>
-      <c r="D13" s="71"/>
-      <c r="E13" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+      <c r="L29" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="30" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="H30" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C14" s="1">
-        <v>13</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+      <c r="L30" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="31" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E31" s="66"/>
+      <c r="F31" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C15" s="1">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="I15" s="77"/>
-      <c r="J15" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="C16" s="1">
-        <v>14</v>
-      </c>
-      <c r="E16" s="72" t="s">
-        <v>229</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="I16" s="77"/>
-      <c r="J16" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="C17" s="1">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="C18" s="1">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
+      <c r="L31" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F32" s="76" t="s">
+        <v>598</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C19" s="1">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
+      <c r="L32" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="33" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F33" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C20" s="1">
-        <v>16</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="7" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C21" s="1">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
+      <c r="L33" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="K34" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C22" s="1">
-        <v>18</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+      <c r="L34" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="K35" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C23" s="1">
-        <v>19</v>
-      </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C24" s="1">
-        <v>20</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="C25" s="1">
-        <v>20</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G25" s="76" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="65"/>
-      <c r="E27" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C28" s="1">
-        <v>22</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C29" s="1">
-        <v>23</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="7" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C30" s="1">
-        <v>23</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C31" s="1">
-        <v>24</v>
-      </c>
-      <c r="D31" s="66"/>
-      <c r="E31" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="1" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C32" s="1">
-        <v>24</v>
-      </c>
-      <c r="E32" s="76" t="s">
+      <c r="L35" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="F38" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C33" s="1">
-        <v>25</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C34" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C35" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="C36" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C37" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="C38" s="1">
-        <v>28</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="G38" s="1" t="s">
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E39" s="63"/>
+      <c r="F39" s="7" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="C39" s="1">
-        <v>29</v>
-      </c>
-      <c r="D39" s="63"/>
-      <c r="E39" s="7" t="s">
+      <c r="H39" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="G39" s="1" t="s">
+    </row>
+    <row r="40" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E40" s="71"/>
+      <c r="F40" s="7" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="C40" s="1">
-        <v>29</v>
-      </c>
-      <c r="D40" s="71"/>
-      <c r="E40" s="7" t="s">
+      <c r="H40" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="G40" s="1" t="s">
+    </row>
+    <row r="41" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E41" s="64"/>
+      <c r="F41" s="7" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C41" s="1">
-        <v>30</v>
-      </c>
-      <c r="D41" s="64"/>
-      <c r="E41" s="7" t="s">
+      <c r="H41" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="G41" s="1" t="s">
+    </row>
+    <row r="42" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E42" s="65"/>
+      <c r="F42" s="7" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="C42" s="1">
-        <v>30</v>
-      </c>
-      <c r="D42" s="65"/>
-      <c r="E42" s="7" t="s">
+      <c r="H42" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="G42" s="1" t="s">
+    </row>
+    <row r="43" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E43" s="66"/>
+      <c r="F43" s="7" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="C43" s="1">
-        <v>32</v>
-      </c>
-      <c r="D43" s="66"/>
-      <c r="E43" s="7" t="s">
+      <c r="H43" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="G43" s="1" t="s">
+    </row>
+    <row r="44" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E44" s="68"/>
+      <c r="F44" s="7" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C44" s="1">
-        <v>32</v>
-      </c>
-      <c r="D44" s="68"/>
-      <c r="E44" s="7" t="s">
+      <c r="H44" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="G44" s="1" t="s">
+    </row>
+    <row r="45" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E45" s="67"/>
+      <c r="F45" s="7" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C45" s="1">
-        <v>33</v>
-      </c>
-      <c r="D45" s="67"/>
-      <c r="E45" s="7" t="s">
+      <c r="H45" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="G45" s="1" t="s">
+    </row>
+    <row r="46" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E46" s="64"/>
+      <c r="F46" s="7" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D46" s="64"/>
-      <c r="E46" s="7" t="s">
+    <row r="47" spans="5:12" x14ac:dyDescent="0.3">
+      <c r="E47" s="65"/>
+      <c r="F47" s="7" t="s">
         <v>616</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="D47" s="65"/>
-      <c r="E47" s="7" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B53" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B55" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B56" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B57" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B58" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B60" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B61" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B64" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B65" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B66" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B67" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -3927,7 +3695,7 @@
   <dimension ref="A1:AD196"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="40" customWidth="1"/>
     <col min="3" max="3" width="13" style="14" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="12.77734375" style="12" customWidth="1"/>
@@ -3952,6 +3720,7 @@
     <col min="23" max="23" width="6.44140625" style="14" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="11.6640625" style="5" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="2.21875" customWidth="1"/>
+    <col min="27" max="27" width="8.88671875" customWidth="1"/>
     <col min="31" max="31" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3973,26 +3742,26 @@
       <c r="G1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="165" t="s">
+      <c r="H1" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="164"/>
-      <c r="J1" s="163" t="s">
+      <c r="I1" s="169"/>
+      <c r="J1" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="164"/>
-      <c r="L1" s="165" t="s">
+      <c r="K1" s="169"/>
+      <c r="L1" s="170" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="164"/>
-      <c r="N1" s="164"/>
-      <c r="O1" s="164"/>
-      <c r="P1" s="165" t="s">
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="164"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="164"/>
+      <c r="Q1" s="169"/>
+      <c r="R1" s="169"/>
+      <c r="S1" s="169"/>
       <c r="T1" s="73" t="s">
         <v>14</v>
       </c>
@@ -4006,7 +3775,7 @@
         <v>17</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Z1" s="123" t="s">
         <v>573</v>
@@ -4134,6 +3903,9 @@
       <c r="X3" s="85" t="s">
         <v>496</v>
       </c>
+      <c r="AA3" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B4" s="78"/>
@@ -4751,7 +4523,7 @@
       </c>
       <c r="W12" s="84"/>
       <c r="X12" s="85" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="Z12" s="58"/>
       <c r="AA12" s="1"/>
@@ -4819,7 +4591,7 @@
       </c>
       <c r="W13" s="84"/>
       <c r="X13" s="85" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="Z13" s="58"/>
       <c r="AA13" s="1"/>
@@ -8286,7 +8058,7 @@
       </c>
       <c r="W64" s="84"/>
       <c r="X64" s="85" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.3">
@@ -8351,7 +8123,7 @@
       <c r="V65" s="101"/>
       <c r="W65" s="84"/>
       <c r="X65" s="85" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.3">
@@ -8890,7 +8662,7 @@
     </row>
     <row r="74" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B74" s="78" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C74" s="119">
         <v>87220455</v>
@@ -8952,7 +8724,7 @@
       </c>
       <c r="W74" s="84"/>
       <c r="X74" s="85" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.3">
@@ -9017,7 +8789,7 @@
       </c>
       <c r="W75" s="84"/>
       <c r="X75" s="85" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.3">
@@ -9692,13 +9464,13 @@
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B86" s="78" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C86" s="119">
         <v>87320125</v>
       </c>
       <c r="D86" s="79" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E86" s="79">
         <v>18</v>
@@ -9738,7 +9510,7 @@
       <c r="R86" s="104"/>
       <c r="S86" s="104"/>
       <c r="T86" s="79" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="U86" s="84"/>
       <c r="V86" s="84" t="s">
@@ -9748,7 +9520,7 @@
         <v>27</v>
       </c>
       <c r="X86" s="85" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.3">
@@ -9807,7 +9579,7 @@
         <v>27</v>
       </c>
       <c r="X87" s="85" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.3">
@@ -9876,7 +9648,7 @@
         <v>27</v>
       </c>
       <c r="X88" s="85" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.3">
@@ -9943,7 +9715,7 @@
         <v>27</v>
       </c>
       <c r="X89" s="85" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.3">
@@ -10010,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="X90" s="85" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.3">
@@ -10077,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="X91" s="85" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.3">
@@ -10144,7 +9916,7 @@
         <v>27</v>
       </c>
       <c r="X92" s="85" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.3">
@@ -10211,7 +9983,7 @@
         <v>27</v>
       </c>
       <c r="X93" s="85" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="94" spans="2:24" x14ac:dyDescent="0.3">
@@ -10276,7 +10048,7 @@
       </c>
       <c r="W94" s="91"/>
       <c r="X94" s="92" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="95" spans="2:24" x14ac:dyDescent="0.3">
@@ -10341,7 +10113,7 @@
       </c>
       <c r="W95" s="91"/>
       <c r="X95" s="92" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="96" spans="2:24" x14ac:dyDescent="0.3">
@@ -10410,7 +10182,7 @@
         <v>27</v>
       </c>
       <c r="X96" s="85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="97" spans="2:24" x14ac:dyDescent="0.3">
@@ -10477,7 +10249,7 @@
         <v>27</v>
       </c>
       <c r="X97" s="85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="98" spans="2:24" x14ac:dyDescent="0.3">
@@ -10544,7 +10316,7 @@
         <v>27</v>
       </c>
       <c r="X98" s="85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="99" spans="2:24" x14ac:dyDescent="0.3">
@@ -10611,7 +10383,7 @@
       </c>
       <c r="W99" s="84"/>
       <c r="X99" s="85" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="100" spans="2:24" x14ac:dyDescent="0.3">
@@ -10676,7 +10448,7 @@
       </c>
       <c r="W100" s="91"/>
       <c r="X100" s="92" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="101" spans="2:24" x14ac:dyDescent="0.3">
@@ -10743,7 +10515,7 @@
       </c>
       <c r="W101" s="99"/>
       <c r="X101" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="102" spans="2:24" x14ac:dyDescent="0.3">
@@ -10810,7 +10582,7 @@
         <v>27</v>
       </c>
       <c r="X102" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="103" spans="2:24" x14ac:dyDescent="0.3">
@@ -10877,7 +10649,7 @@
         <v>27</v>
       </c>
       <c r="X103" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="104" spans="2:24" x14ac:dyDescent="0.3">
@@ -10944,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="X104" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="105" spans="2:24" x14ac:dyDescent="0.3">
@@ -11011,7 +10783,7 @@
         <v>27</v>
       </c>
       <c r="X105" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="106" spans="2:24" x14ac:dyDescent="0.3">
@@ -11078,7 +10850,7 @@
         <v>27</v>
       </c>
       <c r="X106" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="107" spans="2:24" x14ac:dyDescent="0.3">
@@ -11143,7 +10915,7 @@
       </c>
       <c r="W107" s="84"/>
       <c r="X107" s="85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="108" spans="2:24" x14ac:dyDescent="0.3">
@@ -11204,7 +10976,7 @@
         <v>27</v>
       </c>
       <c r="X108" s="85" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="109" spans="2:24" x14ac:dyDescent="0.3">
@@ -11261,7 +11033,7 @@
       </c>
       <c r="W109" s="91"/>
       <c r="X109" s="92" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="110" spans="2:24" x14ac:dyDescent="0.3">
@@ -11330,7 +11102,7 @@
         <v>27</v>
       </c>
       <c r="X110" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="111" spans="2:24" x14ac:dyDescent="0.3">
@@ -11397,7 +11169,7 @@
         <v>27</v>
       </c>
       <c r="X111" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="112" spans="2:24" x14ac:dyDescent="0.3">
@@ -11464,7 +11236,7 @@
         <v>27</v>
       </c>
       <c r="X112" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="113" spans="2:24" x14ac:dyDescent="0.3">
@@ -11529,7 +11301,7 @@
       </c>
       <c r="W113" s="91"/>
       <c r="X113" s="92" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="114" spans="2:24" x14ac:dyDescent="0.3">
@@ -11596,7 +11368,7 @@
         <v>27</v>
       </c>
       <c r="X114" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="115" spans="2:24" x14ac:dyDescent="0.3">
@@ -11653,7 +11425,7 @@
       </c>
       <c r="W115" s="91"/>
       <c r="X115" s="92" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="116" spans="2:24" x14ac:dyDescent="0.3">
@@ -11710,7 +11482,7 @@
       </c>
       <c r="W116" s="91"/>
       <c r="X116" s="92" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="117" spans="2:24" x14ac:dyDescent="0.3">
@@ -11769,7 +11541,7 @@
         <v>27</v>
       </c>
       <c r="X117" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="118" spans="2:24" x14ac:dyDescent="0.3">
@@ -11828,12 +11600,12 @@
         <v>27</v>
       </c>
       <c r="X118" s="85" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="119" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B119" s="78" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C119" s="119">
         <v>17410689</v>
@@ -11895,7 +11667,7 @@
       </c>
       <c r="W119" s="84"/>
       <c r="X119" s="85" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="120" spans="2:24" x14ac:dyDescent="0.3">
@@ -11964,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="X120" s="85" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="121" spans="2:24" x14ac:dyDescent="0.3">
@@ -12031,12 +11803,12 @@
         <v>27</v>
       </c>
       <c r="X121" s="85" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="122" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B122" s="78" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C122" s="119">
         <v>17420178</v>
@@ -12098,7 +11870,7 @@
       </c>
       <c r="W122" s="84"/>
       <c r="X122" s="85" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="123" spans="2:24" x14ac:dyDescent="0.3">
@@ -12163,7 +11935,7 @@
       </c>
       <c r="W123" s="84"/>
       <c r="X123" s="85" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="124" spans="2:24" x14ac:dyDescent="0.3">
@@ -12228,7 +12000,7 @@
       </c>
       <c r="W124" s="84"/>
       <c r="X124" s="85" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="125" spans="2:24" x14ac:dyDescent="0.3">
@@ -12295,7 +12067,7 @@
         <v>27</v>
       </c>
       <c r="X125" s="85" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="126" spans="2:24" x14ac:dyDescent="0.3">
@@ -12362,7 +12134,7 @@
         <v>27</v>
       </c>
       <c r="X126" s="85" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="127" spans="2:24" x14ac:dyDescent="0.3">
@@ -12421,7 +12193,7 @@
         <v>27</v>
       </c>
       <c r="X127" s="85" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="128" spans="2:24" x14ac:dyDescent="0.3">
@@ -12486,7 +12258,7 @@
       </c>
       <c r="W128" s="91"/>
       <c r="X128" s="92" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="129" spans="2:24" x14ac:dyDescent="0.3">
@@ -12551,7 +12323,7 @@
       </c>
       <c r="W129" s="91"/>
       <c r="X129" s="92" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="130" spans="2:24" x14ac:dyDescent="0.3">
@@ -12618,7 +12390,7 @@
       </c>
       <c r="W130" s="84"/>
       <c r="X130" s="85" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="131" spans="2:24" x14ac:dyDescent="0.3">
@@ -12683,7 +12455,7 @@
       </c>
       <c r="W131" s="84"/>
       <c r="X131" s="85" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="132" spans="2:24" x14ac:dyDescent="0.3">
@@ -12750,7 +12522,7 @@
         <v>27</v>
       </c>
       <c r="X132" s="85" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="133" spans="2:24" x14ac:dyDescent="0.3">
@@ -12817,7 +12589,7 @@
         <v>27</v>
       </c>
       <c r="X133" s="85" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="134" spans="2:24" x14ac:dyDescent="0.3">
@@ -12882,7 +12654,7 @@
       </c>
       <c r="W134" s="91"/>
       <c r="X134" s="92" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="135" spans="2:24" x14ac:dyDescent="0.3">
@@ -12947,7 +12719,7 @@
       </c>
       <c r="W135" s="91"/>
       <c r="X135" s="92" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="136" spans="2:24" x14ac:dyDescent="0.3">
@@ -13006,12 +12778,12 @@
         <v>27</v>
       </c>
       <c r="X136" s="85" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="137" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B137" s="86" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C137" s="120">
         <v>17440150</v>
@@ -13073,7 +12845,7 @@
       </c>
       <c r="W137" s="91"/>
       <c r="X137" s="92" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="138" spans="2:24" x14ac:dyDescent="0.3">
@@ -13142,7 +12914,7 @@
         <v>27</v>
       </c>
       <c r="X138" s="85" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="139" spans="2:24" x14ac:dyDescent="0.3">
@@ -13199,7 +12971,7 @@
       </c>
       <c r="W139" s="84"/>
       <c r="X139" s="85" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="140" spans="2:24" x14ac:dyDescent="0.3">
@@ -13266,7 +13038,7 @@
       </c>
       <c r="W140" s="84"/>
       <c r="X140" s="85" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="141" spans="2:24" x14ac:dyDescent="0.3">
@@ -13333,7 +13105,7 @@
       </c>
       <c r="W141" s="84"/>
       <c r="X141" s="85" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="142" spans="2:24" x14ac:dyDescent="0.3">
@@ -13400,7 +13172,7 @@
       </c>
       <c r="W142" s="84"/>
       <c r="X142" s="85" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="143" spans="2:24" x14ac:dyDescent="0.3">
@@ -13467,7 +13239,7 @@
       </c>
       <c r="W143" s="84"/>
       <c r="X143" s="85" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="144" spans="2:24" x14ac:dyDescent="0.3">
@@ -13534,7 +13306,7 @@
       </c>
       <c r="W144" s="84"/>
       <c r="X144" s="85" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="145" spans="2:24" x14ac:dyDescent="0.3">
@@ -13601,7 +13373,7 @@
       </c>
       <c r="W145" s="84"/>
       <c r="X145" s="85" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="146" spans="2:24" x14ac:dyDescent="0.3">
@@ -13670,7 +13442,7 @@
         <v>27</v>
       </c>
       <c r="X146" s="85" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="147" spans="2:24" x14ac:dyDescent="0.3">
@@ -13737,7 +13509,7 @@
         <v>27</v>
       </c>
       <c r="X147" s="85" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="148" spans="2:24" x14ac:dyDescent="0.3">
@@ -13796,7 +13568,7 @@
       </c>
       <c r="W148" s="84"/>
       <c r="X148" s="85" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="149" spans="2:24" x14ac:dyDescent="0.3">
@@ -13855,7 +13627,7 @@
       </c>
       <c r="W149" s="84"/>
       <c r="X149" s="85" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="150" spans="2:24" x14ac:dyDescent="0.3">
@@ -13922,7 +13694,7 @@
       </c>
       <c r="W150" s="84"/>
       <c r="X150" s="85" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="151" spans="2:24" x14ac:dyDescent="0.3">
@@ -13985,12 +13757,12 @@
       <c r="V151" s="115"/>
       <c r="W151" s="91"/>
       <c r="X151" s="92" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="152" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B152" s="78" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C152" s="119">
         <v>17470183</v>
@@ -14044,7 +13816,7 @@
         <v>850</v>
       </c>
       <c r="T152" s="94" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="U152" s="84"/>
       <c r="V152" s="84" t="s">
@@ -14054,7 +13826,7 @@
         <v>27</v>
       </c>
       <c r="X152" s="85" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="153" spans="2:24" x14ac:dyDescent="0.3">
@@ -14121,7 +13893,7 @@
         <v>27</v>
       </c>
       <c r="X153" s="85" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="154" spans="2:24" x14ac:dyDescent="0.3">
@@ -14190,7 +13962,7 @@
         <v>27</v>
       </c>
       <c r="X154" s="85" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="155" spans="2:24" x14ac:dyDescent="0.3">
@@ -14257,12 +14029,12 @@
         <v>27</v>
       </c>
       <c r="X155" s="85" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="156" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B156" s="78" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C156" s="119">
         <v>17460152</v>
@@ -14326,7 +14098,7 @@
         <v>27</v>
       </c>
       <c r="X156" s="85" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="157" spans="2:24" x14ac:dyDescent="0.3">
@@ -14395,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="X157" s="85" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="158" spans="2:24" x14ac:dyDescent="0.3">
@@ -14454,7 +14226,7 @@
         <v>27</v>
       </c>
       <c r="X158" s="92" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="159" spans="2:24" x14ac:dyDescent="0.3">
@@ -14517,7 +14289,7 @@
       </c>
       <c r="W159" s="2"/>
       <c r="X159" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="160" spans="2:24" x14ac:dyDescent="0.3">
@@ -14582,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="X160" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="161" spans="2:24" x14ac:dyDescent="0.3">
@@ -14647,7 +14419,7 @@
         <v>27</v>
       </c>
       <c r="X161" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="162" spans="2:24" x14ac:dyDescent="0.3">
@@ -14704,7 +14476,7 @@
         <v>27</v>
       </c>
       <c r="X162" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="163" spans="2:24" x14ac:dyDescent="0.3">
@@ -14769,7 +14541,7 @@
       </c>
       <c r="W163" s="2"/>
       <c r="X163" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="164" spans="2:24" x14ac:dyDescent="0.3">
@@ -14832,7 +14604,7 @@
       </c>
       <c r="W164" s="2"/>
       <c r="X164" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="165" spans="2:24" x14ac:dyDescent="0.3">
@@ -14897,7 +14669,7 @@
         <v>27</v>
       </c>
       <c r="X165" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="166" spans="2:24" x14ac:dyDescent="0.3">
@@ -14962,7 +14734,7 @@
         <v>27</v>
       </c>
       <c r="X166" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="167" spans="2:24" x14ac:dyDescent="0.3">
@@ -15019,7 +14791,7 @@
         <v>27</v>
       </c>
       <c r="X167" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="168" spans="2:24" x14ac:dyDescent="0.3">
@@ -15086,7 +14858,7 @@
         <v>27</v>
       </c>
       <c r="X168" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="169" spans="2:24" x14ac:dyDescent="0.3">
@@ -15141,7 +14913,7 @@
       </c>
       <c r="W169" s="2"/>
       <c r="X169" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="170" spans="2:24" x14ac:dyDescent="0.3">
@@ -15206,7 +14978,7 @@
       </c>
       <c r="W170" s="2"/>
       <c r="X170" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="171" spans="2:24" x14ac:dyDescent="0.3">
@@ -15271,7 +15043,7 @@
       </c>
       <c r="W171" s="2"/>
       <c r="X171" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="172" spans="2:24" x14ac:dyDescent="0.3">
@@ -15336,7 +15108,7 @@
       </c>
       <c r="W172" s="2"/>
       <c r="X172" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="173" spans="2:24" x14ac:dyDescent="0.3">
@@ -15401,7 +15173,7 @@
       </c>
       <c r="W173" s="2"/>
       <c r="X173" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="174" spans="2:24" x14ac:dyDescent="0.3">
@@ -15466,7 +15238,7 @@
       </c>
       <c r="W174" s="2"/>
       <c r="X174" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="175" spans="2:24" x14ac:dyDescent="0.3">
@@ -15531,7 +15303,7 @@
       </c>
       <c r="W175" s="2"/>
       <c r="X175" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="176" spans="2:24" x14ac:dyDescent="0.3">
@@ -15598,7 +15370,7 @@
         <v>27</v>
       </c>
       <c r="X176" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="177" spans="2:24" x14ac:dyDescent="0.3">
@@ -15663,7 +15435,7 @@
         <v>27</v>
       </c>
       <c r="X177" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="178" spans="2:24" x14ac:dyDescent="0.3">
@@ -15728,16 +15500,16 @@
         <v>27</v>
       </c>
       <c r="X178" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="179" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B179" s="39" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C179" s="30"/>
       <c r="D179" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E179" s="8">
         <v>20</v>
@@ -15785,7 +15557,7 @@
         <v>900</v>
       </c>
       <c r="T179" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="U179" s="2"/>
       <c r="V179" s="2" t="s">
@@ -15795,7 +15567,7 @@
         <v>27</v>
       </c>
       <c r="X179" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="180" spans="2:24" x14ac:dyDescent="0.3">
@@ -15852,7 +15624,7 @@
       </c>
       <c r="W180" s="2"/>
       <c r="X180" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="181" spans="2:24" x14ac:dyDescent="0.3">
@@ -15909,7 +15681,7 @@
       </c>
       <c r="W181" s="2"/>
       <c r="X181" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="182" spans="2:24" x14ac:dyDescent="0.3">
@@ -15974,7 +15746,7 @@
       </c>
       <c r="W182" s="2"/>
       <c r="X182" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="183" spans="2:24" x14ac:dyDescent="0.3">
@@ -16039,12 +15811,12 @@
       </c>
       <c r="W183" s="2"/>
       <c r="X183" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="184" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B184" s="39" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C184" s="30"/>
       <c r="D184" s="8" t="s">
@@ -16096,7 +15868,7 @@
         <v>850</v>
       </c>
       <c r="T184" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="U184" s="2"/>
       <c r="V184" s="2" t="s">
@@ -16106,7 +15878,7 @@
         <v>27</v>
       </c>
       <c r="X184" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="185" spans="2:24" x14ac:dyDescent="0.3">
@@ -16161,7 +15933,7 @@
         <v>760</v>
       </c>
       <c r="T185" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="U185" s="2"/>
       <c r="V185" s="2" t="s">
@@ -16171,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="X185" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="186" spans="2:24" x14ac:dyDescent="0.3">
@@ -16236,12 +16008,12 @@
         <v>27</v>
       </c>
       <c r="X186" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="187" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B187" s="39" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C187" s="30"/>
       <c r="D187" s="8" t="s">
@@ -16293,7 +16065,7 @@
         <v>830</v>
       </c>
       <c r="T187" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="U187" s="2"/>
       <c r="V187" s="2" t="s">
@@ -16303,7 +16075,7 @@
         <v>27</v>
       </c>
       <c r="X187" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="188" spans="2:24" x14ac:dyDescent="0.3">
@@ -16358,7 +16130,7 @@
         <v>900</v>
       </c>
       <c r="T188" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="U188" s="2"/>
       <c r="V188" s="2" t="s">
@@ -16368,7 +16140,7 @@
         <v>27</v>
       </c>
       <c r="X188" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="189" spans="2:24" x14ac:dyDescent="0.3">
@@ -16435,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="X189" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="190" spans="2:24" x14ac:dyDescent="0.3">
@@ -16500,12 +16272,12 @@
         <v>27</v>
       </c>
       <c r="X190" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="191" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B191" s="39" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C191" s="30"/>
       <c r="D191" s="8" t="s">
@@ -16567,7 +16339,7 @@
         <v>27</v>
       </c>
       <c r="X191" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="192" spans="2:24" x14ac:dyDescent="0.3">
@@ -16622,7 +16394,7 @@
         <v>900</v>
       </c>
       <c r="T192" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="U192" s="2"/>
       <c r="V192" s="2" t="s">
@@ -16632,7 +16404,7 @@
         <v>27</v>
       </c>
       <c r="X192" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="193" spans="2:24" x14ac:dyDescent="0.3">
@@ -16699,7 +16471,7 @@
         <v>27</v>
       </c>
       <c r="X193" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="194" spans="2:24" x14ac:dyDescent="0.3">
@@ -16764,7 +16536,7 @@
         <v>27</v>
       </c>
       <c r="X194" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="195" spans="2:24" x14ac:dyDescent="0.3">
@@ -16829,7 +16601,7 @@
         <v>27</v>
       </c>
       <c r="X195" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="196" spans="2:24" x14ac:dyDescent="0.3">
@@ -16886,7 +16658,7 @@
         <v>27</v>
       </c>
       <c r="X196" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -17578,7 +17350,7 @@
       </c>
       <c r="B18" s="54"/>
       <c r="C18" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="44"/>
@@ -18310,7 +18082,7 @@
       <c r="K41" s="141">
         <v>17</v>
       </c>
-      <c r="L41" s="167">
+      <c r="L41" s="164">
         <v>21</v>
       </c>
       <c r="M41" s="141">
@@ -18561,7 +18333,7 @@
       </c>
       <c r="B49" s="54"/>
       <c r="C49" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D49" s="44"/>
       <c r="E49" s="44"/>
@@ -19593,7 +19365,7 @@
       </c>
       <c r="B81" s="54"/>
       <c r="C81" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D81" s="44"/>
       <c r="E81" s="44"/>
@@ -20380,7 +20152,7 @@
       <c r="K106" s="137">
         <v>21</v>
       </c>
-      <c r="L106" s="166">
+      <c r="L106" s="163">
         <v>26</v>
       </c>
       <c r="M106" s="137">
@@ -20759,7 +20531,7 @@
       </c>
       <c r="B116" s="54"/>
       <c r="C116" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D116" s="44"/>
       <c r="E116" s="44"/>
@@ -21898,7 +21670,7 @@
       </c>
       <c r="B152" s="54"/>
       <c r="C152" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D152" s="44"/>
       <c r="E152" s="44"/>
@@ -22167,7 +21939,7 @@
       </c>
       <c r="B161" s="54"/>
       <c r="C161" s="69" t="s">
-        <v>117</v>
+        <v>675</v>
       </c>
       <c r="D161" s="44"/>
       <c r="E161" s="44"/>
@@ -22287,7 +22059,7 @@
       </c>
       <c r="B165" s="54"/>
       <c r="C165" s="69" t="s">
-        <v>120</v>
+        <v>676</v>
       </c>
       <c r="D165" s="44"/>
       <c r="E165" s="44"/>
@@ -22407,7 +22179,7 @@
       </c>
       <c r="B169" s="54"/>
       <c r="C169" s="69" t="s">
-        <v>123</v>
+        <v>677</v>
       </c>
       <c r="D169" s="44"/>
       <c r="E169" s="44"/>
@@ -22889,7 +22661,7 @@
       </c>
       <c r="B183" s="54"/>
       <c r="C183" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D183" s="44"/>
       <c r="E183" s="44"/>
@@ -23713,7 +23485,7 @@
       <c r="K208" s="141">
         <v>10</v>
       </c>
-      <c r="L208" s="167">
+      <c r="L208" s="164">
         <v>13</v>
       </c>
       <c r="M208" s="141">
@@ -23962,7 +23734,7 @@
       </c>
       <c r="B216" s="54"/>
       <c r="C216" s="69" t="s">
-        <v>43</v>
+        <v>666</v>
       </c>
       <c r="D216" s="44"/>
       <c r="E216" s="44"/>
@@ -25236,7 +25008,7 @@
       </c>
       <c r="B254" s="54"/>
       <c r="C254" s="69" t="s">
-        <v>156</v>
+        <v>666</v>
       </c>
       <c r="D254" s="44"/>
       <c r="E254" s="44"/>
@@ -26099,7 +25871,7 @@
       <c r="K280" s="137">
         <v>18</v>
       </c>
-      <c r="L280" s="166">
+      <c r="L280" s="163">
         <v>22</v>
       </c>
       <c r="M280" s="137">
@@ -27218,7 +26990,7 @@
       </c>
       <c r="B302" s="54"/>
       <c r="C302" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D302" s="44"/>
       <c r="E302" s="44"/>
@@ -28225,7 +27997,7 @@
       <c r="K333" s="141">
         <v>15</v>
       </c>
-      <c r="L333" s="167">
+      <c r="L333" s="164">
         <v>19</v>
       </c>
       <c r="M333" s="141">
@@ -28468,7 +28240,7 @@
       </c>
       <c r="B341" s="54"/>
       <c r="C341" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D341" s="44"/>
       <c r="E341" s="44"/>
@@ -28795,7 +28567,7 @@
       </c>
       <c r="B352" s="54"/>
       <c r="C352" s="69" t="s">
-        <v>223</v>
+        <v>678</v>
       </c>
       <c r="D352" s="44"/>
       <c r="E352" s="44"/>
@@ -28915,7 +28687,7 @@
       </c>
       <c r="B356" s="54"/>
       <c r="C356" s="69" t="s">
-        <v>226</v>
+        <v>679</v>
       </c>
       <c r="D356" s="44"/>
       <c r="E356" s="44"/>
@@ -29644,7 +29416,7 @@
       <c r="K372" s="141">
         <v>17</v>
       </c>
-      <c r="L372" s="167">
+      <c r="L372" s="164">
         <v>21</v>
       </c>
       <c r="M372" s="141">
@@ -29706,7 +29478,7 @@
       <c r="K373" s="141">
         <v>17</v>
       </c>
-      <c r="L373" s="167">
+      <c r="L373" s="164">
         <v>21</v>
       </c>
       <c r="M373" s="141">
@@ -29957,7 +29729,7 @@
       </c>
       <c r="B381" s="54"/>
       <c r="C381" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D381" s="44"/>
       <c r="E381" s="44"/>
@@ -31136,7 +30908,7 @@
       </c>
       <c r="B416" s="54"/>
       <c r="C416" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D416" s="44"/>
       <c r="E416" s="44"/>
@@ -31463,7 +31235,7 @@
       </c>
       <c r="B427" s="54"/>
       <c r="C427" s="69" t="s">
-        <v>258</v>
+        <v>680</v>
       </c>
       <c r="D427" s="44"/>
       <c r="E427" s="44"/>
@@ -31583,7 +31355,7 @@
       </c>
       <c r="B431" s="54"/>
       <c r="C431" s="69" t="s">
-        <v>261</v>
+        <v>681</v>
       </c>
       <c r="D431" s="44"/>
       <c r="E431" s="44"/>
@@ -31703,7 +31475,7 @@
       </c>
       <c r="B435" s="54"/>
       <c r="C435" s="69" t="s">
-        <v>264</v>
+        <v>682</v>
       </c>
       <c r="D435" s="44"/>
       <c r="E435" s="44"/>
@@ -32002,7 +31774,7 @@
       <c r="K442" s="141">
         <v>23</v>
       </c>
-      <c r="L442" s="167">
+      <c r="L442" s="164">
         <v>28</v>
       </c>
       <c r="M442" s="141">
@@ -32253,7 +32025,7 @@
       </c>
       <c r="B450" s="54"/>
       <c r="C450" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D450" s="44"/>
       <c r="E450" s="44"/>
@@ -33212,7 +32984,7 @@
       <c r="K477" s="141">
         <v>13</v>
       </c>
-      <c r="L477" s="167">
+      <c r="L477" s="164">
         <v>16</v>
       </c>
       <c r="M477" s="141">
@@ -33336,7 +33108,7 @@
       <c r="K479" s="141">
         <v>16</v>
       </c>
-      <c r="L479" s="167">
+      <c r="L479" s="164">
         <v>20</v>
       </c>
       <c r="M479" s="141">
@@ -33390,7 +33162,7 @@
       <c r="K480" s="141">
         <v>17</v>
       </c>
-      <c r="L480" s="167">
+      <c r="L480" s="164">
         <v>21</v>
       </c>
       <c r="M480" s="141">
@@ -33741,7 +33513,7 @@
       </c>
       <c r="B490" s="54"/>
       <c r="C490" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D490" s="44"/>
       <c r="E490" s="44"/>
@@ -34917,7 +34689,7 @@
       <c r="K521" s="141">
         <v>13</v>
       </c>
-      <c r="L521" s="167">
+      <c r="L521" s="164">
         <v>16</v>
       </c>
       <c r="M521" s="141">
@@ -35168,7 +34940,7 @@
       </c>
       <c r="B529" s="54"/>
       <c r="C529" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D529" s="44"/>
       <c r="E529" s="44"/>
@@ -36264,7 +36036,7 @@
       </c>
       <c r="B563" s="54"/>
       <c r="C563" s="69" t="s">
-        <v>43</v>
+        <v>667</v>
       </c>
       <c r="D563" s="44"/>
       <c r="E563" s="44"/>
@@ -37395,7 +37167,7 @@
       <c r="K593" s="141">
         <v>23</v>
       </c>
-      <c r="L593" s="167">
+      <c r="L593" s="164">
         <v>29</v>
       </c>
       <c r="M593" s="141">
@@ -37458,7 +37230,7 @@
       <c r="K594" s="141">
         <v>21</v>
       </c>
-      <c r="L594" s="167">
+      <c r="L594" s="164">
         <v>26</v>
       </c>
       <c r="M594" s="141">
@@ -37713,7 +37485,7 @@
       </c>
       <c r="B602" s="54"/>
       <c r="C602" s="69" t="s">
-        <v>43</v>
+        <v>668</v>
       </c>
       <c r="D602" s="44"/>
       <c r="E602" s="44"/>
@@ -38069,7 +37841,7 @@
       </c>
       <c r="B614" s="54"/>
       <c r="C614" s="69" t="s">
-        <v>333</v>
+        <v>683</v>
       </c>
       <c r="D614" s="44"/>
       <c r="E614" s="44"/>
@@ -38189,7 +37961,7 @@
       </c>
       <c r="B618" s="54"/>
       <c r="C618" s="69" t="s">
-        <v>336</v>
+        <v>684</v>
       </c>
       <c r="D618" s="44"/>
       <c r="E618" s="44"/>
@@ -38794,7 +38566,7 @@
       <c r="K632" s="141">
         <v>17</v>
       </c>
-      <c r="L632" s="167">
+      <c r="L632" s="164">
         <v>21</v>
       </c>
       <c r="M632" s="141">
@@ -38856,7 +38628,7 @@
       <c r="K633" s="141">
         <v>19</v>
       </c>
-      <c r="L633" s="167">
+      <c r="L633" s="164">
         <v>24</v>
       </c>
       <c r="M633" s="141">
@@ -39161,7 +38933,7 @@
       </c>
       <c r="B642" s="54"/>
       <c r="C642" s="69" t="s">
-        <v>43</v>
+        <v>668</v>
       </c>
       <c r="D642" s="44"/>
       <c r="E642" s="44"/>
@@ -40087,7 +39859,7 @@
       <c r="K670" s="141">
         <v>14</v>
       </c>
-      <c r="L670" s="167">
+      <c r="L670" s="164">
         <v>17</v>
       </c>
       <c r="M670" s="141">
@@ -40271,7 +40043,7 @@
       <c r="K673" s="11">
         <v>23</v>
       </c>
-      <c r="L673" s="168">
+      <c r="L673" s="165">
         <v>29</v>
       </c>
       <c r="M673" s="11">
@@ -40580,7 +40352,7 @@
       </c>
       <c r="B682" s="54"/>
       <c r="C682" s="69" t="s">
-        <v>43</v>
+        <v>669</v>
       </c>
       <c r="D682" s="44"/>
       <c r="E682" s="44"/>
@@ -41559,7 +41331,7 @@
       <c r="K710" s="137">
         <v>23</v>
       </c>
-      <c r="L710" s="166">
+      <c r="L710" s="163">
         <v>29</v>
       </c>
       <c r="M710" s="137">
@@ -41751,7 +41523,7 @@
       <c r="K713" s="137">
         <v>23</v>
       </c>
-      <c r="L713" s="166">
+      <c r="L713" s="163">
         <v>29</v>
       </c>
       <c r="M713" s="137">
@@ -42060,7 +41832,7 @@
       </c>
       <c r="B722" s="54"/>
       <c r="C722" s="69" t="s">
-        <v>43</v>
+        <v>669</v>
       </c>
       <c r="D722" s="44"/>
       <c r="E722" s="44"/>
@@ -43181,7 +42953,7 @@
       </c>
       <c r="B756" s="54"/>
       <c r="C756" s="69" t="s">
-        <v>43</v>
+        <v>670</v>
       </c>
       <c r="D756" s="44"/>
       <c r="E756" s="44"/>
@@ -44383,7 +44155,7 @@
       </c>
       <c r="B794" s="54"/>
       <c r="C794" s="69" t="s">
-        <v>43</v>
+        <v>671</v>
       </c>
       <c r="D794" s="44"/>
       <c r="E794" s="44"/>
@@ -45354,7 +45126,9 @@
         <v>42</v>
       </c>
       <c r="B825" s="54"/>
-      <c r="C825" s="69"/>
+      <c r="C825" s="69" t="s">
+        <v>671</v>
+      </c>
       <c r="D825" s="44"/>
       <c r="E825" s="44"/>
       <c r="F825" s="44"/>
@@ -46202,7 +45976,7 @@
       <c r="K850" s="141">
         <v>21</v>
       </c>
-      <c r="L850" s="167">
+      <c r="L850" s="164">
         <v>26</v>
       </c>
       <c r="M850" s="141">
@@ -46453,7 +46227,7 @@
       </c>
       <c r="B858" s="54"/>
       <c r="C858" s="69" t="s">
-        <v>43</v>
+        <v>671</v>
       </c>
       <c r="D858" s="44"/>
       <c r="E858" s="44"/>
@@ -47398,7 +47172,7 @@
       </c>
       <c r="B888" s="54"/>
       <c r="C888" s="69" t="s">
-        <v>43</v>
+        <v>671</v>
       </c>
       <c r="D888" s="44"/>
       <c r="E888" s="44"/>
@@ -48123,7 +47897,7 @@
       <c r="K911" s="137">
         <v>14</v>
       </c>
-      <c r="L911" s="166">
+      <c r="L911" s="163">
         <v>17</v>
       </c>
       <c r="M911" s="137">
@@ -48620,7 +48394,7 @@
       </c>
       <c r="B923" s="54"/>
       <c r="C923" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D923" s="44"/>
       <c r="E923" s="44"/>
@@ -49718,7 +49492,7 @@
       </c>
       <c r="B956" s="54"/>
       <c r="C956" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D956" s="44"/>
       <c r="E956" s="44"/>
@@ -50727,7 +50501,7 @@
       </c>
       <c r="B987" s="54"/>
       <c r="C987" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D987" s="44"/>
       <c r="E987" s="44"/>
@@ -51452,7 +51226,7 @@
       <c r="K1010" s="137">
         <v>21</v>
       </c>
-      <c r="L1010" s="166">
+      <c r="L1010" s="163">
         <v>26</v>
       </c>
       <c r="M1010" s="137">
@@ -51703,7 +51477,7 @@
       </c>
       <c r="B1018" s="54"/>
       <c r="C1018" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1018" s="44"/>
       <c r="E1018" s="44"/>
@@ -52399,7 +52173,7 @@
       <c r="K1040" s="137">
         <v>18</v>
       </c>
-      <c r="L1040" s="166">
+      <c r="L1040" s="163">
         <v>22</v>
       </c>
       <c r="M1040" s="137">
@@ -52523,7 +52297,7 @@
       <c r="K1042" s="137">
         <v>21</v>
       </c>
-      <c r="L1042" s="166">
+      <c r="L1042" s="163">
         <v>26</v>
       </c>
       <c r="M1042" s="137">
@@ -52585,7 +52359,7 @@
       <c r="K1043" s="137">
         <v>21</v>
       </c>
-      <c r="L1043" s="166">
+      <c r="L1043" s="163">
         <v>26</v>
       </c>
       <c r="M1043" s="137">
@@ -52960,7 +52734,7 @@
       </c>
       <c r="B1053" s="54"/>
       <c r="C1053" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1053" s="44"/>
       <c r="E1053" s="44"/>
@@ -54122,7 +53896,7 @@
       </c>
       <c r="B1087" s="54"/>
       <c r="C1087" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1087" s="44"/>
       <c r="E1087" s="44"/>
@@ -54880,7 +54654,7 @@
       <c r="K1110" s="137">
         <v>23</v>
       </c>
-      <c r="L1110" s="166">
+      <c r="L1110" s="163">
         <v>29</v>
       </c>
       <c r="M1110" s="137">
@@ -55255,7 +55029,7 @@
       </c>
       <c r="B1120" s="54"/>
       <c r="C1120" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1120" s="44"/>
       <c r="E1120" s="44"/>
@@ -55951,7 +55725,7 @@
       <c r="K1142" s="137">
         <v>23</v>
       </c>
-      <c r="L1142" s="166">
+      <c r="L1142" s="163">
         <v>29</v>
       </c>
       <c r="M1142" s="137">
@@ -56013,7 +55787,7 @@
       <c r="K1143" s="137">
         <v>23</v>
       </c>
-      <c r="L1143" s="166">
+      <c r="L1143" s="163">
         <v>29</v>
       </c>
       <c r="M1143" s="137">
@@ -56264,7 +56038,7 @@
       </c>
       <c r="B1151" s="54"/>
       <c r="C1151" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1151" s="44"/>
       <c r="E1151" s="44"/>
@@ -56989,7 +56763,7 @@
       <c r="K1174" s="137">
         <v>21</v>
       </c>
-      <c r="L1174" s="166">
+      <c r="L1174" s="163">
         <v>26</v>
       </c>
       <c r="M1174" s="137">
@@ -57051,7 +56825,7 @@
       <c r="K1175" s="137">
         <v>21</v>
       </c>
-      <c r="L1175" s="166">
+      <c r="L1175" s="163">
         <v>26</v>
       </c>
       <c r="M1175" s="137">
@@ -57302,7 +57076,7 @@
       </c>
       <c r="B1183" s="54"/>
       <c r="C1183" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1183" s="44"/>
       <c r="E1183" s="44"/>
@@ -58367,7 +58141,7 @@
       </c>
       <c r="B1215" s="54"/>
       <c r="C1215" s="69" t="s">
-        <v>43</v>
+        <v>672</v>
       </c>
       <c r="D1215" s="44"/>
       <c r="E1215" s="44"/>
@@ -59218,7 +58992,7 @@
       <c r="K1240" s="141">
         <v>15</v>
       </c>
-      <c r="L1240" s="167">
+      <c r="L1240" s="164">
         <v>19</v>
       </c>
       <c r="M1240" s="141">
@@ -59463,7 +59237,9 @@
         <v>42</v>
       </c>
       <c r="B1248" s="54"/>
-      <c r="C1248" s="69"/>
+      <c r="C1248" s="69" t="s">
+        <v>671</v>
+      </c>
       <c r="D1248" s="44"/>
       <c r="E1248" s="44"/>
       <c r="F1248" s="44"/>
@@ -60309,7 +60085,7 @@
       <c r="K1273" s="137">
         <v>23</v>
       </c>
-      <c r="L1273" s="166">
+      <c r="L1273" s="163">
         <v>29</v>
       </c>
       <c r="M1273" s="137">
@@ -60560,7 +60336,7 @@
       </c>
       <c r="B1281" s="54"/>
       <c r="C1281" s="69" t="s">
-        <v>43</v>
+        <v>673</v>
       </c>
       <c r="D1281" s="44"/>
       <c r="E1281" s="44"/>
@@ -61500,7 +61276,7 @@
       <c r="K1308" s="137">
         <v>21</v>
       </c>
-      <c r="L1308" s="166">
+      <c r="L1308" s="163">
         <v>26</v>
       </c>
       <c r="M1308" s="137">
@@ -61562,7 +61338,7 @@
       <c r="K1309" s="137">
         <v>21</v>
       </c>
-      <c r="L1309" s="166">
+      <c r="L1309" s="163">
         <v>26</v>
       </c>
       <c r="M1309" s="137">
@@ -61686,7 +61462,7 @@
       <c r="K1311" s="137">
         <v>21</v>
       </c>
-      <c r="L1311" s="166">
+      <c r="L1311" s="163">
         <v>26</v>
       </c>
       <c r="M1311" s="137">
@@ -61748,7 +61524,7 @@
       <c r="K1312" s="137">
         <v>21</v>
       </c>
-      <c r="L1312" s="166">
+      <c r="L1312" s="163">
         <v>26</v>
       </c>
       <c r="M1312" s="137">
@@ -62123,7 +61899,7 @@
       </c>
       <c r="B1322" s="54"/>
       <c r="C1322" s="69" t="s">
-        <v>43</v>
+        <v>673</v>
       </c>
       <c r="D1322" s="44"/>
       <c r="E1322" s="44"/>
@@ -63218,7 +62994,7 @@
       <c r="K1351" s="141">
         <v>18</v>
       </c>
-      <c r="L1351" s="167">
+      <c r="L1351" s="164">
         <v>22</v>
       </c>
       <c r="M1351" s="141">
@@ -63839,7 +63615,7 @@
       </c>
       <c r="B1365" s="54"/>
       <c r="C1365" s="69" t="s">
-        <v>43</v>
+        <v>673</v>
       </c>
       <c r="D1365" s="44"/>
       <c r="E1365" s="44"/>
@@ -64630,7 +64406,7 @@
       <c r="K1388" s="90">
         <v>17</v>
       </c>
-      <c r="L1388" s="169">
+      <c r="L1388" s="166">
         <v>21</v>
       </c>
       <c r="M1388" s="90">
@@ -65033,7 +64809,9 @@
         <v>42</v>
       </c>
       <c r="B1399" s="54"/>
-      <c r="C1399" s="69"/>
+      <c r="C1399" s="69" t="s">
+        <v>673</v>
+      </c>
       <c r="D1399" s="44"/>
       <c r="E1399" s="44"/>
       <c r="F1399" s="44"/>
@@ -65907,7 +65685,7 @@
       <c r="K1424" s="137">
         <v>23</v>
       </c>
-      <c r="L1424" s="166">
+      <c r="L1424" s="163">
         <v>29</v>
       </c>
       <c r="M1424" s="137">
@@ -66276,7 +66054,7 @@
       </c>
       <c r="B1434" s="54"/>
       <c r="C1434" s="69" t="s">
-        <v>43</v>
+        <v>673</v>
       </c>
       <c r="D1434" s="44"/>
       <c r="E1434" s="44"/>
@@ -67285,7 +67063,7 @@
       </c>
       <c r="B1465" s="54"/>
       <c r="C1465" s="69" t="s">
-        <v>43</v>
+        <v>673</v>
       </c>
       <c r="D1465" s="44"/>
       <c r="E1465" s="44"/>
@@ -68391,7 +68169,7 @@
       </c>
       <c r="B1498" s="54"/>
       <c r="C1498" s="69" t="s">
-        <v>43</v>
+        <v>674</v>
       </c>
       <c r="D1498" s="44"/>
       <c r="E1498" s="44"/>
@@ -69433,7 +69211,7 @@
       </c>
       <c r="B1530" s="54"/>
       <c r="C1530" s="69" t="s">
-        <v>43</v>
+        <v>674</v>
       </c>
       <c r="D1530" s="44"/>
       <c r="E1530" s="44"/>
@@ -70475,7 +70253,7 @@
       </c>
       <c r="B1562" s="54"/>
       <c r="C1562" s="69" t="s">
-        <v>43</v>
+        <v>674</v>
       </c>
       <c r="D1562" s="44"/>
       <c r="E1562" s="44"/>
@@ -71016,17 +70794,17 @@
       <c r="Y1580" s="44"/>
     </row>
     <row r="1600" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z1600" s="170">
+      <c r="Z1600" s="167">
         <v>16</v>
       </c>
     </row>
     <row r="1601" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z1601" s="170">
+      <c r="Z1601" s="167">
         <v>18.3</v>
       </c>
     </row>
     <row r="1602" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z1602" s="170">
+      <c r="Z1602" s="167">
         <v>21</v>
       </c>
     </row>
